--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.57249742094797</v>
+        <v>4.643030830904046</v>
       </c>
       <c r="D2" t="n">
-        <v>28.26402552298295</v>
+        <v>4.592904147484729</v>
       </c>
       <c r="E2" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F2" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.77447356695569</v>
+        <v>3.050851954630299</v>
       </c>
       <c r="D3" t="n">
-        <v>19.00965311748349</v>
+        <v>3.089068631591067</v>
       </c>
       <c r="E3" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F3" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.66197427492936</v>
+        <v>4.982570819676022</v>
       </c>
       <c r="D4" t="n">
-        <v>31.25625538350604</v>
+        <v>5.079141499819732</v>
       </c>
       <c r="E4" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F4" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.845572775903651</v>
+        <v>1.437405576084343</v>
       </c>
       <c r="D5" t="n">
-        <v>8.665129741061598</v>
+        <v>1.40808358292251</v>
       </c>
       <c r="E5" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F5" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.56362088772644</v>
+        <v>5.779088394255547</v>
       </c>
       <c r="D6" t="n">
-        <v>34.54857930844151</v>
+        <v>5.614144137621746</v>
       </c>
       <c r="E6" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F6" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54357653111568</v>
+        <v>2.850831186306299</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3601155558454</v>
+        <v>2.008518777824877</v>
       </c>
       <c r="E7" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F7" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.03180978433499</v>
+        <v>2.117669089954436</v>
       </c>
       <c r="D8" t="n">
-        <v>3.554897168859197</v>
+        <v>0.5776707899396196</v>
       </c>
       <c r="E8" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F8" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.67532168052581</v>
+        <v>6.934739773085445</v>
       </c>
       <c r="D9" t="n">
-        <v>32.87150673135262</v>
+        <v>5.341619843844802</v>
       </c>
       <c r="E9" t="n">
-        <v>10.98317712858219</v>
+        <v>1.784766283394606</v>
       </c>
       <c r="F9" t="n">
-        <v>11.27354769112024</v>
+        <v>1.83195149980704</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
